--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:10:08+00:00</t>
+    <t>2026-09-03T05:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:17:43+00:00</t>
+    <t>2026-09-03T05:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T05:48:26+00:00</t>
+    <t>2026-09-03T10:47:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:47:18+00:00</t>
+    <t>2026-09-08T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-alpha.6</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:02:02+00:00</t>
+    <t>2026-09-09T10:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:10:08+00:00</t>
+    <t>2026-09-09T13:56:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:56:56+00:00</t>
+    <t>2026-09-09T14:11:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:11:38+00:00</t>
+    <t>2026-09-09T14:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:19:13+00:00</t>
+    <t>2026-09-09T14:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:42:29+00:00</t>
+    <t>2026-09-09T15:55:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5733" uniqueCount="445">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:55:32+00:00</t>
+    <t>2026-09-10T12:50:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -634,73 +634,109 @@
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.Untersuchungsmethode</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie</t>
-  </si>
-  <si>
-    <t>Mikroskopie</t>
-  </si>
-  <si>
-    <t>Morphologische Beobachtung von Mikroorganismen mittels mikroskopischer Untersuchung, ohne taxonomische Identifikation.</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.id</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.Untersuchungscode</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie</t>
+  </si>
+  <si>
+    <t>Allgemeine Mikroskopie</t>
+  </si>
+  <si>
+    <t>Morphologische Beobachtung von Mikroorganismen mittels mikroskopischer Untersuchung. Das Ergebnis ist eine morphologische Gruppe, keine Spezies.</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.Untersuchungscode</t>
   </si>
   <si>
     <t>Kodierung der Untersuchung; mikroskopische Beobachtung (LOINC).</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.Ergebnis</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.Ergebnis</t>
   </si>
   <si>
     <t>Beobachtete Morphologie (SNOMED CT).</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Mikroskopie.Untersuchungsmethode</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.Untersuchungsmethode</t>
   </si>
   <si>
     <t>Eingesetztes mikroskopisches Verfahren einschließlich Färbetechnik, z. B. Gramfärbung (SNOMED CT).</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore</t>
-  </si>
-  <si>
-    <t>Barlett Score</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie</t>
+  </si>
+  <si>
+    <t>Spezifische Mikroskopie</t>
+  </si>
+  <si>
+    <t>Mikroskopischer Nachweis eines im Untersuchungscode benannten Objekts mit der semiquantitativen Stufe als Ergebnis.</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Untersuchungscode</t>
+  </si>
+  <si>
+    <t>Kodierung des gesuchten Objekts und der Färbetechnik (LOINC, ordinale Skala).</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Ergebnis</t>
+  </si>
+  <si>
+    <t>Semiquantitative Stufe, in der das gesuchte Objekt gesehen wurde (SNOMED CT).</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Untersuchungsmethode</t>
+  </si>
+  <si>
+    <t>Eingesetzte Färbetechnik, entbehrlich wenn sie bereits im Untersuchungscode steht (SNOMED CT).</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore</t>
+  </si>
+  <si>
+    <t>Bartlett Score</t>
   </si>
   <si>
     <t>Qualitative mikroskopische Beurteilung der Eignung von Sputumproben für die Kultur anhand des Verhältnisses von Entzündungs- zu Epithelzellen.</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.id</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.Untersuchungscode</t>
-  </si>
-  <si>
-    <t>Kodierung der Untersuchung; hier fest: Barlett-Score (LOINC).</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.Ergebnis</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.id</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.Untersuchungscode</t>
+  </si>
+  <si>
+    <t>Kodierung der Untersuchung; hier fest: Bartlett-Score (LOINC).</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.Ergebnis</t>
   </si>
   <si>
     <t>Score-Kategorie und daraus abgeleitete Eignung der Probe (LOINC).</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BarlettScore.Untersuchungsmethode</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore.Untersuchungsmethode</t>
   </si>
   <si>
     <t>Eingesetztes Verfahren; hier fest: Mikroskopie (SNOMED CT).</t>
@@ -812,10 +848,14 @@
     <t>Getestete antimikrobielle Substanz und Testverfahren (LOINC). Es werden bevorzugt Codes ohne präkoordinierte Probenart verwendet.</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Empfindlichkeit.Ergebnis</t>
-  </si>
-  <si>
-    <t>Gemessener Wert der Empfindlichkeitstestung, z. B. minimale Hemmkonzentration in mg/L oder Hemmhofdurchmesser in mm (UCUM).</t>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Empfindlichkeit.Ergebnis[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Gemessener Wert der Empfindlichkeitstestung, z. B. minimale Hemmkonzentration in mg/L oder Hemmhofdurchmesser in mm (UCUM) — oder, wenn nicht gemessen wurde, die Empfindlichkeitskategorie.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.Empfindlichkeit.Bewertung</t>
@@ -1633,7 +1673,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ174"/>
+  <dimension ref="A1:AJ181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="97.9765625" customWidth="true" bestFit="true"/>
@@ -7455,13 +7495,13 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7529,10 +7569,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7561,7 +7601,7 @@
         <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7612,7 +7652,7 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8161,13 +8201,13 @@
         <v>73</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8235,10 +8275,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8264,10 +8304,10 @@
         <v>180</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8318,7 +8358,7 @@
         <v>73</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -8335,10 +8375,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8349,7 +8389,7 @@
         <v>74</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>73</v>
@@ -8361,10 +8401,10 @@
         <v>73</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>187</v>
+        <v>249</v>
       </c>
       <c r="M67" t="s" s="2">
         <v>250</v>
@@ -8418,19 +8458,19 @@
         <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
@@ -8449,7 +8489,7 @@
         <v>74</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>73</v>
@@ -8461,13 +8501,13 @@
         <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>252</v>
+        <v>85</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8518,38 +8558,38 @@
         <v>73</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>73</v>
@@ -8561,15 +8601,17 @@
         <v>73</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>73</v>
@@ -8606,43 +8648,43 @@
         <v>73</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8655,24 +8697,26 @@
         <v>73</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>73</v>
       </c>
@@ -8708,19 +8752,19 @@
         <v>73</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -8737,46 +8781,42 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>73</v>
       </c>
@@ -8824,27 +8864,27 @@
         <v>73</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8852,7 +8892,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>83</v>
@@ -8867,13 +8907,13 @@
         <v>73</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8924,10 +8964,10 @@
         <v>73</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>83</v>
@@ -8941,10 +8981,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8967,10 +9007,10 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>184</v>
+        <v>259</v>
       </c>
       <c r="M73" t="s" s="2">
         <v>260</v>
@@ -9024,7 +9064,7 @@
         <v>73</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -9067,10 +9107,10 @@
         <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>262</v>
@@ -9136,7 +9176,7 @@
         <v>73</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75">
@@ -9155,7 +9195,7 @@
         <v>74</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>73</v>
@@ -9167,13 +9207,13 @@
         <v>73</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>85</v>
+        <v>264</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9224,38 +9264,38 @@
         <v>73</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>87</v>
+        <v>263</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>73</v>
@@ -9267,17 +9307,15 @@
         <v>73</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>73</v>
@@ -9314,43 +9352,43 @@
         <v>73</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9363,26 +9401,24 @@
         <v>73</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O77" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>73</v>
       </c>
@@ -9418,19 +9454,19 @@
         <v>73</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -9447,42 +9483,46 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>267</v>
+        <v>150</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>73</v>
       </c>
@@ -9530,19 +9570,19 @@
         <v>73</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>266</v>
+        <v>153</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79">
@@ -9576,10 +9616,10 @@
         <v>180</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9647,10 +9687,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9661,7 +9701,7 @@
         <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>73</v>
@@ -9673,13 +9713,13 @@
         <v>73</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9730,27 +9770,27 @@
         <v>73</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9773,13 +9813,13 @@
         <v>73</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>85</v>
+        <v>259</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>86</v>
+        <v>275</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9830,7 +9870,7 @@
         <v>73</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>87</v>
+        <v>274</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -9842,7 +9882,7 @@
         <v>73</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
@@ -9854,14 +9894,14 @@
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>73</v>
@@ -9873,17 +9913,15 @@
         <v>73</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>73</v>
@@ -9920,31 +9958,31 @@
         <v>73</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83">
@@ -9956,7 +9994,7 @@
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -9969,26 +10007,24 @@
         <v>73</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O83" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>73</v>
       </c>
@@ -10024,19 +10060,19 @@
         <v>73</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10060,7 +10096,7 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10073,22 +10109,26 @@
         <v>73</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>73</v>
       </c>
@@ -10136,7 +10176,7 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>278</v>
+        <v>153</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10148,15 +10188,15 @@
         <v>73</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10164,7 +10204,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>83</v>
@@ -10179,13 +10219,13 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>86</v>
+        <v>281</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10236,10 +10276,10 @@
         <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>87</v>
+        <v>279</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>83</v>
@@ -10260,14 +10300,14 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>73</v>
@@ -10279,17 +10319,15 @@
         <v>73</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>91</v>
+        <v>283</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>73</v>
@@ -10326,43 +10364,43 @@
         <v>73</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>97</v>
+        <v>282</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10375,26 +10413,22 @@
         <v>73</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>150</v>
+        <v>286</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>73</v>
       </c>
@@ -10442,7 +10476,7 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>153</v>
+        <v>285</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -10454,15 +10488,15 @@
         <v>73</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10470,7 +10504,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>83</v>
@@ -10485,13 +10519,13 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>285</v>
+        <v>86</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10542,10 +10576,10 @@
         <v>73</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>284</v>
+        <v>87</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>83</v>
@@ -10559,21 +10593,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>73</v>
@@ -10585,15 +10619,17 @@
         <v>73</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>73</v>
@@ -10630,71 +10666,75 @@
         <v>73</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>73</v>
       </c>
@@ -10742,27 +10782,27 @@
         <v>73</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>288</v>
+        <v>153</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10788,10 +10828,10 @@
         <v>141</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10842,7 +10882,7 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
@@ -10859,10 +10899,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10959,10 +10999,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11061,10 +11101,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11165,10 +11205,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11197,7 +11237,7 @@
         <v>181</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11248,7 +11288,7 @@
         <v>73</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -11265,10 +11305,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11297,7 +11337,7 @@
         <v>184</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11348,7 +11388,7 @@
         <v>73</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -11365,10 +11405,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11397,7 +11437,7 @@
         <v>187</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11448,7 +11488,7 @@
         <v>73</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -11465,10 +11505,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11494,10 +11534,10 @@
         <v>141</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11548,7 +11588,7 @@
         <v>73</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -11565,10 +11605,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11665,10 +11705,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11767,10 +11807,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11871,10 +11911,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11903,7 +11943,7 @@
         <v>181</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11954,7 +11994,7 @@
         <v>73</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -11971,10 +12011,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11997,13 +12037,13 @@
         <v>73</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12054,7 +12094,7 @@
         <v>73</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12071,10 +12111,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12103,7 +12143,7 @@
         <v>187</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12154,7 +12194,7 @@
         <v>73</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -12171,10 +12211,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12197,13 +12237,13 @@
         <v>73</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12254,7 +12294,7 @@
         <v>73</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
@@ -12266,15 +12306,15 @@
         <v>73</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12285,7 +12325,7 @@
         <v>74</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>73</v>
@@ -12297,13 +12337,13 @@
         <v>73</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>318</v>
+        <v>85</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>319</v>
+        <v>86</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12354,38 +12394,38 @@
         <v>73</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>317</v>
+        <v>87</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>73</v>
@@ -12397,15 +12437,17 @@
         <v>73</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>73</v>
@@ -12442,43 +12484,43 @@
         <v>73</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -12491,24 +12533,26 @@
         <v>73</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>73</v>
       </c>
@@ -12544,19 +12588,19 @@
         <v>73</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -12573,46 +12617,42 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>73</v>
       </c>
@@ -12660,19 +12700,19 @@
         <v>73</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>153</v>
+        <v>321</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110">
@@ -12691,7 +12731,7 @@
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>73</v>
@@ -12703,13 +12743,13 @@
         <v>73</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="L110" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12766,21 +12806,21 @@
         <v>74</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12803,13 +12843,13 @@
         <v>73</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>86</v>
+        <v>326</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12860,7 +12900,7 @@
         <v>73</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>87</v>
+        <v>325</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -12884,7 +12924,7 @@
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -12903,17 +12943,15 @@
         <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>91</v>
+        <v>328</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>73</v>
@@ -12950,19 +12988,19 @@
         <v>73</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>97</v>
+        <v>327</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -12974,19 +13012,19 @@
         <v>73</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -12999,26 +13037,22 @@
         <v>73</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>150</v>
+        <v>331</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>73</v>
       </c>
@@ -13066,7 +13100,7 @@
         <v>73</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>153</v>
+        <v>330</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13078,15 +13112,15 @@
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13094,7 +13128,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>83</v>
@@ -13109,13 +13143,13 @@
         <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>330</v>
+        <v>86</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13166,10 +13200,10 @@
         <v>73</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>329</v>
+        <v>87</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>83</v>
@@ -13183,21 +13217,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -13209,15 +13243,17 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>73</v>
@@ -13254,43 +13290,43 @@
         <v>73</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>331</v>
+        <v>97</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -13303,22 +13339,26 @@
         <v>73</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>334</v>
+        <v>150</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O116" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>73</v>
       </c>
@@ -13366,7 +13406,7 @@
         <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>333</v>
+        <v>153</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -13378,7 +13418,7 @@
         <v>73</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="117">
@@ -13397,7 +13437,7 @@
         <v>74</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>73</v>
@@ -13409,13 +13449,13 @@
         <v>73</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>85</v>
+        <v>337</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>86</v>
+        <v>338</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13466,38 +13506,38 @@
         <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>87</v>
+        <v>336</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
@@ -13509,17 +13549,15 @@
         <v>73</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>73</v>
@@ -13556,43 +13594,43 @@
         <v>73</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -13605,26 +13643,24 @@
         <v>73</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O119" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>73</v>
       </c>
@@ -13660,19 +13696,19 @@
         <v>73</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -13689,42 +13725,46 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>73</v>
       </c>
@@ -13772,27 +13812,27 @@
         <v>73</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>339</v>
+        <v>153</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13800,7 +13840,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>83</v>
@@ -13818,10 +13858,10 @@
         <v>180</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13872,10 +13912,10 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>83</v>
@@ -13889,10 +13929,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13918,10 +13958,10 @@
         <v>180</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>301</v>
+        <v>345</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13972,7 +14012,7 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
@@ -13989,10 +14029,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14018,10 +14058,10 @@
         <v>141</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14072,7 +14112,7 @@
         <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -14089,10 +14129,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14189,10 +14229,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14291,10 +14331,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14395,10 +14435,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14427,7 +14467,7 @@
         <v>181</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14478,7 +14518,7 @@
         <v>73</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -14495,10 +14535,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14527,7 +14567,7 @@
         <v>184</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14578,7 +14618,7 @@
         <v>73</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
@@ -14595,10 +14635,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14609,7 +14649,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14621,13 +14661,13 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>354</v>
+        <v>187</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>355</v>
+        <v>314</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14678,19 +14718,19 @@
         <v>73</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130">
@@ -14709,7 +14749,7 @@
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>73</v>
@@ -14721,13 +14761,13 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>85</v>
+        <v>357</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>86</v>
+        <v>358</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14778,38 +14818,38 @@
         <v>73</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>87</v>
+        <v>356</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>73</v>
@@ -14821,17 +14861,15 @@
         <v>73</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>73</v>
@@ -14868,43 +14906,43 @@
         <v>73</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -14917,26 +14955,24 @@
         <v>73</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O132" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>73</v>
       </c>
@@ -14972,19 +15008,19 @@
         <v>73</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -15001,42 +15037,46 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>73</v>
       </c>
@@ -15084,27 +15124,27 @@
         <v>73</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>359</v>
+        <v>153</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15112,7 +15152,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>83</v>
@@ -15130,10 +15170,10 @@
         <v>180</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15184,10 +15224,10 @@
         <v>73</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>83</v>
@@ -15201,10 +15241,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15215,7 +15255,7 @@
         <v>74</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>73</v>
@@ -15227,10 +15267,10 @@
         <v>73</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>364</v>
+        <v>184</v>
       </c>
       <c r="M135" t="s" s="2">
         <v>365</v>
@@ -15284,19 +15324,19 @@
         <v>73</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136">
@@ -15315,7 +15355,7 @@
         <v>74</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>73</v>
@@ -15327,13 +15367,13 @@
         <v>73</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>85</v>
+        <v>367</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>86</v>
+        <v>368</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15384,38 +15424,38 @@
         <v>73</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>87</v>
+        <v>366</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>73</v>
@@ -15427,17 +15467,15 @@
         <v>73</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>73</v>
@@ -15474,43 +15512,43 @@
         <v>73</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -15523,26 +15561,24 @@
         <v>73</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O138" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>73</v>
       </c>
@@ -15578,19 +15614,19 @@
         <v>73</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -15607,42 +15643,46 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>73</v>
       </c>
@@ -15690,27 +15730,27 @@
         <v>73</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>369</v>
+        <v>153</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15718,7 +15758,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>83</v>
@@ -15736,10 +15776,10 @@
         <v>180</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -15790,10 +15830,10 @@
         <v>73</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>83</v>
@@ -15807,10 +15847,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15821,7 +15861,7 @@
         <v>74</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>73</v>
@@ -15833,10 +15873,10 @@
         <v>73</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>374</v>
+        <v>184</v>
       </c>
       <c r="M141" t="s" s="2">
         <v>375</v>
@@ -15890,13 +15930,13 @@
         <v>73</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>73</v>
@@ -16439,7 +16479,7 @@
         <v>73</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>184</v>
@@ -16527,7 +16567,7 @@
         <v>74</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>73</v>
@@ -16539,13 +16579,13 @@
         <v>73</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>247</v>
+        <v>387</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16602,7 +16642,7 @@
         <v>74</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>73</v>
@@ -16613,10 +16653,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16627,7 +16667,7 @@
         <v>74</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>73</v>
@@ -16639,13 +16679,13 @@
         <v>73</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>187</v>
+        <v>390</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -16696,27 +16736,27 @@
         <v>73</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16727,7 +16767,7 @@
         <v>74</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>73</v>
@@ -16739,13 +16779,13 @@
         <v>73</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>391</v>
+        <v>85</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>392</v>
+        <v>86</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16796,19 +16836,19 @@
         <v>73</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>390</v>
+        <v>87</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="151">
@@ -16820,14 +16860,14 @@
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>73</v>
@@ -16839,15 +16879,17 @@
         <v>73</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N151" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N151" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>73</v>
@@ -16884,31 +16926,31 @@
         <v>73</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="152">
@@ -16920,7 +16962,7 @@
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -16933,24 +16975,26 @@
         <v>73</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O152" s="2"/>
+      <c r="O152" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>73</v>
       </c>
@@ -16986,19 +17030,19 @@
         <v>73</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -17022,39 +17066,35 @@
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>73</v>
       </c>
@@ -17102,27 +17142,27 @@
         <v>73</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>153</v>
+        <v>395</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17133,7 +17173,7 @@
         <v>74</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>73</v>
@@ -17145,10 +17185,10 @@
         <v>73</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>397</v>
+        <v>184</v>
       </c>
       <c r="M154" t="s" s="2">
         <v>398</v>
@@ -17202,19 +17242,19 @@
         <v>73</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155">
@@ -17245,13 +17285,13 @@
         <v>73</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>85</v>
+        <v>259</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>86</v>
+        <v>400</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17302,7 +17342,7 @@
         <v>73</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>87</v>
+        <v>399</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>74</v>
@@ -17319,21 +17359,21 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>73</v>
@@ -17345,17 +17385,15 @@
         <v>73</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>73</v>
@@ -17392,43 +17430,43 @@
         <v>73</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>97</v>
+        <v>401</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -17441,26 +17479,22 @@
         <v>73</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>150</v>
+        <v>404</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>73</v>
       </c>
@@ -17508,7 +17542,7 @@
         <v>73</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>153</v>
+        <v>403</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>74</v>
@@ -17520,15 +17554,15 @@
         <v>73</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17536,7 +17570,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>83</v>
@@ -17551,13 +17585,13 @@
         <v>73</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>403</v>
+        <v>86</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17608,10 +17642,10 @@
         <v>73</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>402</v>
+        <v>87</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>83</v>
@@ -17625,21 +17659,21 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>73</v>
@@ -17651,15 +17685,17 @@
         <v>73</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N159" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>73</v>
@@ -17696,71 +17732,75 @@
         <v>73</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N160" s="2"/>
-      <c r="O160" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O160" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P160" t="s" s="2">
         <v>73</v>
       </c>
@@ -17808,27 +17848,27 @@
         <v>73</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>406</v>
+        <v>153</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17854,10 +17894,10 @@
         <v>141</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -17908,7 +17948,7 @@
         <v>73</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>74</v>
@@ -17925,10 +17965,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18025,10 +18065,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18127,10 +18167,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18231,10 +18271,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18263,7 +18303,7 @@
         <v>181</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -18314,7 +18354,7 @@
         <v>73</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>83</v>
@@ -18331,10 +18371,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18357,13 +18397,13 @@
         <v>73</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>416</v>
+        <v>245</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18414,7 +18454,7 @@
         <v>73</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>74</v>
@@ -18431,10 +18471,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18463,7 +18503,7 @@
         <v>187</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18514,7 +18554,7 @@
         <v>73</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>74</v>
@@ -19063,13 +19103,13 @@
         <v>73</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="L173" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19137,10 +19177,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19169,7 +19209,7 @@
         <v>187</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19220,7 +19260,7 @@
         <v>73</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>74</v>
@@ -19232,6 +19272,712 @@
         <v>73</v>
       </c>
       <c r="AJ174" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E177" s="2"/>
+      <c r="F177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K177" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L177" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M177" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N177" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O177" s="2"/>
+      <c r="P177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q177" s="2"/>
+      <c r="R177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB177" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC177" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE177" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF177" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG177" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH177" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI177" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ177" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E178" s="2"/>
+      <c r="F178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I178" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="J178" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="K178" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M178" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N178" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O178" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="P178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q178" s="2"/>
+      <c r="R178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF178" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AG178" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH178" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI178" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ178" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E179" s="2"/>
+      <c r="F179" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K179" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L179" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M179" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
+      <c r="P179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q179" s="2"/>
+      <c r="R179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF179" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG179" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH179" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI179" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ179" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E180" s="2"/>
+      <c r="F180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K180" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L180" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N180" s="2"/>
+      <c r="O180" s="2"/>
+      <c r="P180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q180" s="2"/>
+      <c r="R180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF180" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG180" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH180" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI180" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ180" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E181" s="2"/>
+      <c r="F181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K181" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L181" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M181" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N181" s="2"/>
+      <c r="O181" s="2"/>
+      <c r="P181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q181" s="2"/>
+      <c r="R181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF181" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG181" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH181" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI181" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ181" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:50:06+00:00</t>
+    <t>2026-09-10T13:10:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:10:47+00:00</t>
+    <t>2026-09-10T13:32:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:32:54+00:00</t>
+    <t>2026-09-10T13:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:47:44+00:00</t>
+    <t>2026-09-10T16:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:40:19+00:00</t>
+    <t>2026-09-10T17:22:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:22:53+00:00</t>
+    <t>2026-09-10T17:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:39:40+00:00</t>
+    <t>2026-09-10T18:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T18:06:33+00:00</t>
+    <t>2026-09-11T06:33:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T06:33:50+00:00</t>
+    <t>2026-09-11T11:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:07:28+00:00</t>
+    <t>2026-09-11T11:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T11:48:22+00:00</t>
+    <t>2026-09-11T12:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:41:50+00:00</t>
+    <t>2026-09-11T12:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5733" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="434">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:56:10+00:00</t>
+    <t>2026-09-12T16:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -601,39 +601,6 @@
     <t>Eingesetztes Kulturverfahren (SNOMED CT).</t>
   </si>
   <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur</t>
-  </si>
-  <si>
-    <t>Spezifische Kultur</t>
-  </si>
-  <si>
-    <t>Ergebnis einer zielgerichteten mikrobiologischen Kultur, die prüft, ob ein vordefinierter Mikroorganismus in der Probe wächst.</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.id</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.Untersuchungscode</t>
-  </si>
-  <si>
-    <t>Kodierung des gesuchten Mikroorganismus und des Kulturverfahrens (LOINC).</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.Ergebnis</t>
-  </si>
-  <si>
-    <t>Wachstum oder kein Wachstum des gesuchten Mikroorganismus (SNOMED CT). Ein unbestimmbares Ergebnis wird nicht hier, sondern über den Grund für fehlende Daten abgebildet.</t>
-  </si>
-  <si>
-    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeKultur.Untersuchungsmethode</t>
-  </si>
-  <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie</t>
   </si>
   <si>
@@ -951,7 +918,7 @@
     <t>Spezifische Bestimmung</t>
   </si>
   <si>
-    <t>Qualitativer Nachweis eines vordefinierten mikrobiellen Ziels, kulturbasiert oder mittels molekularer, immunologischer oder biochemischer Verfahren.</t>
+    <t>Qualitativer Nachweis eines vordefinierten mikrobiellen Ziels, kulturbasiert oder mittels molekularer, immunologischer oder biochemischer Verfahren. Das eingesetzte Verfahren steht im Untersuchungscode und in der Untersuchungsmethode, nicht im Ergebnis.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Bestimmung.SpezifischeBestimmung.id</t>
@@ -1673,7 +1640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ181"/>
+  <dimension ref="A1:AJ174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="97.9765625" customWidth="true" bestFit="true"/>
@@ -5483,7 +5450,7 @@
         <v>187</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5551,10 +5518,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5580,10 +5547,10 @@
         <v>141</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5634,7 +5601,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5651,10 +5618,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5751,10 +5718,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5853,10 +5820,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5957,10 +5924,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5989,7 +5956,7 @@
         <v>181</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6040,7 +6007,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -6057,10 +6024,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6089,7 +6056,7 @@
         <v>184</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6140,7 +6107,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6157,10 +6124,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6189,7 +6156,7 @@
         <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6240,7 +6207,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6257,10 +6224,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6286,10 +6253,10 @@
         <v>141</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6340,7 +6307,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6357,10 +6324,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6457,10 +6424,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6559,10 +6526,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6663,10 +6630,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6695,7 +6662,7 @@
         <v>181</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6746,7 +6713,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -6763,10 +6730,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6795,7 +6762,7 @@
         <v>184</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6846,7 +6813,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6863,10 +6830,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6895,7 +6862,7 @@
         <v>187</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6946,7 +6913,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -6963,10 +6930,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6992,10 +6959,10 @@
         <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7046,7 +7013,7 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7063,10 +7030,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7163,10 +7130,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7265,10 +7232,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7369,10 +7336,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7401,7 +7368,7 @@
         <v>181</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7452,7 +7419,7 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -7469,10 +7436,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7495,13 +7462,13 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7552,7 +7519,7 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -7569,10 +7536,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7601,7 +7568,7 @@
         <v>187</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7652,7 +7619,7 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -7669,10 +7636,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7698,10 +7665,10 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7752,7 +7719,7 @@
         <v>73</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -7769,10 +7736,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7869,10 +7836,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7971,10 +7938,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8075,10 +8042,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8107,7 +8074,7 @@
         <v>181</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8158,7 +8125,7 @@
         <v>73</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -8175,10 +8142,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8201,7 +8168,7 @@
         <v>73</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>184</v>
@@ -8258,7 +8225,7 @@
         <v>73</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8304,10 +8271,10 @@
         <v>180</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8375,10 +8342,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8389,7 +8356,7 @@
         <v>74</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>73</v>
@@ -8401,13 +8368,13 @@
         <v>73</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8458,27 +8425,27 @@
         <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8489,7 +8456,7 @@
         <v>74</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>73</v>
@@ -8501,13 +8468,13 @@
         <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>86</v>
+        <v>254</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8558,38 +8525,38 @@
         <v>73</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>87</v>
+        <v>252</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>73</v>
@@ -8601,17 +8568,15 @@
         <v>73</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>73</v>
@@ -8648,43 +8613,43 @@
         <v>73</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8697,26 +8662,24 @@
         <v>73</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K70" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O70" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>73</v>
       </c>
@@ -8752,19 +8715,19 @@
         <v>73</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -8781,42 +8744,46 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>73</v>
       </c>
@@ -8864,27 +8831,27 @@
         <v>73</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>254</v>
+        <v>153</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8892,7 +8859,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>83</v>
@@ -8907,13 +8874,13 @@
         <v>73</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8964,10 +8931,10 @@
         <v>73</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>83</v>
@@ -8981,10 +8948,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9007,13 +8974,13 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>180</v>
+        <v>261</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>259</v>
+        <v>184</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9064,7 +9031,7 @@
         <v>73</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -9081,10 +9048,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9107,13 +9074,13 @@
         <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>187</v>
+        <v>248</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9164,7 +9131,7 @@
         <v>73</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -9176,15 +9143,15 @@
         <v>73</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9195,7 +9162,7 @@
         <v>74</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>73</v>
@@ -9207,13 +9174,13 @@
         <v>73</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>264</v>
+        <v>85</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>265</v>
+        <v>86</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9264,19 +9231,19 @@
         <v>73</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>263</v>
+        <v>87</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76">
@@ -9288,14 +9255,14 @@
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>73</v>
@@ -9307,15 +9274,17 @@
         <v>73</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>73</v>
@@ -9352,31 +9321,31 @@
         <v>73</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77">
@@ -9388,7 +9357,7 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -9401,24 +9370,26 @@
         <v>73</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>73</v>
       </c>
@@ -9454,19 +9425,19 @@
         <v>73</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -9490,39 +9461,35 @@
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>150</v>
+        <v>269</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>73</v>
       </c>
@@ -9570,27 +9537,27 @@
         <v>73</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>153</v>
+        <v>268</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9616,10 +9583,10 @@
         <v>180</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9670,7 +9637,7 @@
         <v>73</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -9687,10 +9654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9701,7 +9668,7 @@
         <v>74</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>73</v>
@@ -9713,13 +9680,13 @@
         <v>73</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>272</v>
+        <v>141</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>184</v>
+        <v>275</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9770,27 +9737,27 @@
         <v>73</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9813,13 +9780,13 @@
         <v>73</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9870,7 +9837,7 @@
         <v>73</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>274</v>
+        <v>87</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -9882,26 +9849,26 @@
         <v>73</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>73</v>
@@ -9913,15 +9880,17 @@
         <v>73</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>73</v>
@@ -9958,43 +9927,43 @@
         <v>73</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10007,24 +9976,26 @@
         <v>73</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K83" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>73</v>
       </c>
@@ -10060,19 +10031,19 @@
         <v>73</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10089,14 +10060,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10109,26 +10080,22 @@
         <v>73</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>150</v>
+        <v>281</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>73</v>
       </c>
@@ -10176,7 +10143,7 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10188,15 +10155,15 @@
         <v>73</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10204,7 +10171,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>83</v>
@@ -10219,13 +10186,13 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>281</v>
+        <v>86</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10276,10 +10243,10 @@
         <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>279</v>
+        <v>87</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>83</v>
@@ -10293,21 +10260,21 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>73</v>
@@ -10319,15 +10286,17 @@
         <v>73</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>73</v>
@@ -10364,31 +10333,31 @@
         <v>73</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>282</v>
+        <v>97</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="87">
@@ -10400,7 +10369,7 @@
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -10413,22 +10382,26 @@
         <v>73</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>286</v>
+        <v>150</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>73</v>
       </c>
@@ -10476,7 +10449,7 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>285</v>
+        <v>153</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -10488,15 +10461,15 @@
         <v>73</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10504,7 +10477,7 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>83</v>
@@ -10519,13 +10492,13 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>86</v>
+        <v>287</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10576,10 +10549,10 @@
         <v>73</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>87</v>
+        <v>286</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>83</v>
@@ -10593,21 +10566,21 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>73</v>
@@ -10619,17 +10592,15 @@
         <v>73</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>73</v>
@@ -10666,31 +10637,31 @@
         <v>73</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>97</v>
+        <v>288</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90">
@@ -10702,39 +10673,35 @@
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>73</v>
       </c>
@@ -10782,27 +10749,27 @@
         <v>73</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>153</v>
+        <v>290</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10828,10 +10795,10 @@
         <v>141</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10882,7 +10849,7 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
@@ -10899,10 +10866,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10999,10 +10966,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11101,10 +11068,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11205,10 +11172,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11237,7 +11204,7 @@
         <v>181</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11288,7 +11255,7 @@
         <v>73</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -11305,10 +11272,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11337,7 +11304,7 @@
         <v>184</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11388,7 +11355,7 @@
         <v>73</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -11405,10 +11372,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11437,7 +11404,7 @@
         <v>187</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11488,7 +11455,7 @@
         <v>73</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -11505,10 +11472,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11534,10 +11501,10 @@
         <v>141</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11588,7 +11555,7 @@
         <v>73</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -11605,10 +11572,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11705,10 +11672,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11807,10 +11774,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11911,10 +11878,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11943,7 +11910,7 @@
         <v>181</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11994,7 +11961,7 @@
         <v>73</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -12011,10 +11978,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12037,13 +12004,13 @@
         <v>73</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="L103" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12094,7 +12061,7 @@
         <v>73</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12111,10 +12078,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12143,7 +12110,7 @@
         <v>187</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12194,7 +12161,7 @@
         <v>73</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -12211,10 +12178,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12237,13 +12204,13 @@
         <v>73</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12294,7 +12261,7 @@
         <v>73</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
@@ -12306,15 +12273,15 @@
         <v>73</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12325,7 +12292,7 @@
         <v>74</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>73</v>
@@ -12337,13 +12304,13 @@
         <v>73</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>86</v>
+        <v>321</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12394,38 +12361,38 @@
         <v>73</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>87</v>
+        <v>319</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>73</v>
@@ -12437,17 +12404,15 @@
         <v>73</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>73</v>
@@ -12484,43 +12449,43 @@
         <v>73</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -12533,26 +12498,24 @@
         <v>73</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K108" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O108" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>73</v>
       </c>
@@ -12588,19 +12551,19 @@
         <v>73</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -12617,42 +12580,46 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>73</v>
       </c>
@@ -12700,27 +12667,27 @@
         <v>73</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>321</v>
+        <v>153</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12731,7 +12698,7 @@
         <v>74</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>73</v>
@@ -12743,13 +12710,13 @@
         <v>73</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>184</v>
+        <v>326</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12800,27 +12767,27 @@
         <v>73</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12843,13 +12810,13 @@
         <v>73</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>326</v>
+        <v>86</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12900,7 +12867,7 @@
         <v>73</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>325</v>
+        <v>87</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -12917,14 +12884,14 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -12943,15 +12910,17 @@
         <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>328</v>
+        <v>91</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>73</v>
@@ -12988,19 +12957,19 @@
         <v>73</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>327</v>
+        <v>97</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13012,7 +12981,7 @@
         <v>73</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="113">
@@ -13024,7 +12993,7 @@
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -13037,22 +13006,26 @@
         <v>73</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>331</v>
+        <v>150</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P113" t="s" s="2">
         <v>73</v>
       </c>
@@ -13100,7 +13073,7 @@
         <v>73</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>330</v>
+        <v>153</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13112,15 +13085,15 @@
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13128,7 +13101,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>83</v>
@@ -13143,13 +13116,13 @@
         <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>86</v>
+        <v>332</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13200,10 +13173,10 @@
         <v>73</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>87</v>
+        <v>331</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>83</v>
@@ -13217,21 +13190,21 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -13243,17 +13216,15 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>73</v>
@@ -13290,31 +13261,31 @@
         <v>73</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>97</v>
+        <v>333</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
@@ -13326,7 +13297,7 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -13339,26 +13310,22 @@
         <v>73</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>150</v>
+        <v>336</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>73</v>
       </c>
@@ -13406,7 +13373,7 @@
         <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>153</v>
+        <v>335</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -13418,15 +13385,15 @@
         <v>73</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13437,7 +13404,7 @@
         <v>74</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>73</v>
@@ -13449,13 +13416,13 @@
         <v>73</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>337</v>
+        <v>85</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>338</v>
+        <v>86</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13506,19 +13473,19 @@
         <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>336</v>
+        <v>87</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118">
@@ -13530,14 +13497,14 @@
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
@@ -13549,15 +13516,17 @@
         <v>73</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>73</v>
@@ -13594,31 +13563,31 @@
         <v>73</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119">
@@ -13630,7 +13599,7 @@
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -13643,24 +13612,26 @@
         <v>73</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K119" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N119" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O119" s="2"/>
+      <c r="O119" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P119" t="s" s="2">
         <v>73</v>
       </c>
@@ -13696,19 +13667,19 @@
         <v>73</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -13732,39 +13703,35 @@
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>73</v>
       </c>
@@ -13812,27 +13779,27 @@
         <v>73</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>153</v>
+        <v>341</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13840,7 +13807,7 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
         <v>83</v>
@@ -13858,10 +13825,10 @@
         <v>180</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13912,10 +13879,10 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>83</v>
@@ -13958,10 +13925,10 @@
         <v>180</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>345</v>
+        <v>303</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14029,10 +13996,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14058,10 +14025,10 @@
         <v>141</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14112,7 +14079,7 @@
         <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -14129,10 +14096,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14229,10 +14196,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14331,10 +14298,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14435,10 +14402,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14467,7 +14434,7 @@
         <v>181</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14518,7 +14485,7 @@
         <v>73</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>83</v>
@@ -14535,10 +14502,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14567,7 +14534,7 @@
         <v>184</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14618,7 +14585,7 @@
         <v>73</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
@@ -14649,7 +14616,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14661,13 +14628,13 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>187</v>
+        <v>356</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>314</v>
+        <v>357</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14724,21 +14691,21 @@
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14749,7 +14716,7 @@
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>73</v>
@@ -14761,13 +14728,13 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>357</v>
+        <v>85</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>358</v>
+        <v>86</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14818,19 +14785,19 @@
         <v>73</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>356</v>
+        <v>87</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131">
@@ -14842,14 +14809,14 @@
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>73</v>
@@ -14861,15 +14828,17 @@
         <v>73</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>73</v>
@@ -14906,31 +14875,31 @@
         <v>73</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="132">
@@ -14942,7 +14911,7 @@
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -14955,24 +14924,26 @@
         <v>73</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K132" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N132" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O132" s="2"/>
+      <c r="O132" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>73</v>
       </c>
@@ -15008,19 +14979,19 @@
         <v>73</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -15044,39 +15015,35 @@
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>73</v>
       </c>
@@ -15124,27 +15091,27 @@
         <v>73</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>153</v>
+        <v>361</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15152,7 +15119,7 @@
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G134" t="s" s="2">
         <v>83</v>
@@ -15170,10 +15137,10 @@
         <v>180</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15224,10 +15191,10 @@
         <v>73</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>83</v>
@@ -15241,10 +15208,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15255,7 +15222,7 @@
         <v>74</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>73</v>
@@ -15267,13 +15234,13 @@
         <v>73</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>184</v>
+        <v>366</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15324,27 +15291,27 @@
         <v>73</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15355,7 +15322,7 @@
         <v>74</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>73</v>
@@ -15367,13 +15334,13 @@
         <v>73</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>367</v>
+        <v>85</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>368</v>
+        <v>86</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15424,19 +15391,19 @@
         <v>73</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>366</v>
+        <v>87</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137">
@@ -15448,14 +15415,14 @@
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>73</v>
@@ -15467,15 +15434,17 @@
         <v>73</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>73</v>
@@ -15512,31 +15481,31 @@
         <v>73</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="138">
@@ -15548,7 +15517,7 @@
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -15561,24 +15530,26 @@
         <v>73</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>73</v>
       </c>
@@ -15614,19 +15585,19 @@
         <v>73</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -15650,39 +15621,35 @@
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>73</v>
       </c>
@@ -15730,27 +15697,27 @@
         <v>73</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>153</v>
+        <v>371</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15758,7 +15725,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>83</v>
@@ -15776,10 +15743,10 @@
         <v>180</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -15830,10 +15797,10 @@
         <v>73</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>83</v>
@@ -15847,10 +15814,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15861,7 +15828,7 @@
         <v>74</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>73</v>
@@ -15873,13 +15840,13 @@
         <v>73</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>184</v>
+        <v>376</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -15930,13 +15897,13 @@
         <v>73</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>73</v>
@@ -15947,10 +15914,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -15976,10 +15943,10 @@
         <v>141</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16030,7 +15997,7 @@
         <v>73</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -16047,10 +16014,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16147,10 +16114,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16249,10 +16216,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16353,10 +16320,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16385,7 +16352,7 @@
         <v>181</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16436,7 +16403,7 @@
         <v>73</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>83</v>
@@ -16453,10 +16420,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16479,13 +16446,13 @@
         <v>73</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="L147" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -16536,7 +16503,7 @@
         <v>73</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -16553,10 +16520,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16567,7 +16534,7 @@
         <v>74</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>73</v>
@@ -16579,13 +16546,13 @@
         <v>73</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>387</v>
+        <v>248</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16636,13 +16603,13 @@
         <v>73</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>73</v>
@@ -16653,10 +16620,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16667,7 +16634,7 @@
         <v>74</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>73</v>
@@ -16679,10 +16646,10 @@
         <v>73</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>390</v>
+        <v>187</v>
       </c>
       <c r="M149" t="s" s="2">
         <v>391</v>
@@ -16736,19 +16703,19 @@
         <v>73</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="150">
@@ -16767,7 +16734,7 @@
         <v>74</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>73</v>
@@ -16779,13 +16746,13 @@
         <v>73</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>85</v>
+        <v>393</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>86</v>
+        <v>394</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16836,38 +16803,38 @@
         <v>73</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>87</v>
+        <v>392</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>73</v>
@@ -16879,17 +16846,15 @@
         <v>73</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>73</v>
@@ -16926,43 +16891,43 @@
         <v>73</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -16975,26 +16940,24 @@
         <v>73</v>
       </c>
       <c r="I152" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K152" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O152" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>73</v>
       </c>
@@ -17030,19 +16993,19 @@
         <v>73</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -17059,42 +17022,46 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>73</v>
       </c>
@@ -17142,27 +17109,27 @@
         <v>73</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>395</v>
+        <v>153</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17173,7 +17140,7 @@
         <v>74</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>73</v>
@@ -17185,13 +17152,13 @@
         <v>73</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>245</v>
+        <v>141</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>184</v>
+        <v>399</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17242,27 +17209,27 @@
         <v>73</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17285,13 +17252,13 @@
         <v>73</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>259</v>
+        <v>85</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>400</v>
+        <v>86</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
@@ -17342,7 +17309,7 @@
         <v>73</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>399</v>
+        <v>87</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>74</v>
@@ -17359,21 +17326,21 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>73</v>
@@ -17385,15 +17352,17 @@
         <v>73</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N156" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>73</v>
@@ -17430,31 +17399,31 @@
         <v>73</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>401</v>
+        <v>97</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="157">
@@ -17466,7 +17435,7 @@
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -17479,22 +17448,26 @@
         <v>73</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>404</v>
+        <v>150</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N157" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O157" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P157" t="s" s="2">
         <v>73</v>
       </c>
@@ -17542,7 +17515,7 @@
         <v>73</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>403</v>
+        <v>153</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>74</v>
@@ -17554,15 +17527,15 @@
         <v>73</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17570,7 +17543,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>83</v>
@@ -17585,13 +17558,13 @@
         <v>73</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>85</v>
+        <v>181</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>86</v>
+        <v>405</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17642,10 +17615,10 @@
         <v>73</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>87</v>
+        <v>404</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>83</v>
@@ -17659,21 +17632,21 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>73</v>
@@ -17685,17 +17658,15 @@
         <v>73</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>73</v>
@@ -17732,31 +17703,31 @@
         <v>73</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>97</v>
+        <v>406</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="160">
@@ -17768,39 +17739,35 @@
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J160" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O160" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>73</v>
       </c>
@@ -17848,19 +17815,19 @@
         <v>73</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>153</v>
+        <v>408</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="161">
@@ -18397,13 +18364,13 @@
         <v>73</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>245</v>
+        <v>418</v>
       </c>
       <c r="L166" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18471,10 +18438,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18503,7 +18470,7 @@
         <v>187</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18554,7 +18521,7 @@
         <v>73</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>74</v>
@@ -18571,10 +18538,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18600,10 +18567,10 @@
         <v>141</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18654,7 +18621,7 @@
         <v>73</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>74</v>
@@ -18671,10 +18638,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18771,10 +18738,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18873,10 +18840,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -18977,10 +18944,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19009,7 +18976,7 @@
         <v>181</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19060,7 +19027,7 @@
         <v>73</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>83</v>
@@ -19077,10 +19044,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19103,13 +19070,13 @@
         <v>73</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>429</v>
+        <v>234</v>
       </c>
       <c r="L173" t="s" s="2">
         <v>184</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19160,7 +19127,7 @@
         <v>73</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>74</v>
@@ -19177,10 +19144,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19209,7 +19176,7 @@
         <v>187</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19260,7 +19227,7 @@
         <v>73</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>74</v>
@@ -19272,712 +19239,6 @@
         <v>73</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="C175" s="2"/>
-      <c r="D175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E175" s="2"/>
-      <c r="F175" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G175" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K175" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="L175" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="M175" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N175" s="2"/>
-      <c r="O175" s="2"/>
-      <c r="P175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q175" s="2"/>
-      <c r="R175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF175" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AG175" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH175" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI175" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ175" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="C176" s="2"/>
-      <c r="D176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E176" s="2"/>
-      <c r="F176" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G176" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K176" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="M176" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
-      <c r="P176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q176" s="2"/>
-      <c r="R176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH176" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI176" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ176" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C177" s="2"/>
-      <c r="D177" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="E177" s="2"/>
-      <c r="F177" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G177" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K177" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="M177" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O177" s="2"/>
-      <c r="P177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q177" s="2"/>
-      <c r="R177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB177" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC177" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE177" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF177" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG177" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH177" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI177" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ177" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C178" s="2"/>
-      <c r="D178" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E178" s="2"/>
-      <c r="F178" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G178" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I178" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="J178" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="K178" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="M178" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="P178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q178" s="2"/>
-      <c r="R178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF178" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AG178" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH178" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI178" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ178" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C179" s="2"/>
-      <c r="D179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E179" s="2"/>
-      <c r="F179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K179" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L179" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M179" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N179" s="2"/>
-      <c r="O179" s="2"/>
-      <c r="P179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q179" s="2"/>
-      <c r="R179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AG179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH179" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI179" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ179" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C180" s="2"/>
-      <c r="D180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E180" s="2"/>
-      <c r="F180" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G180" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K180" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N180" s="2"/>
-      <c r="O180" s="2"/>
-      <c r="P180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q180" s="2"/>
-      <c r="R180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AG180" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH180" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI180" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ180" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="B181" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C181" s="2"/>
-      <c r="D181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E181" s="2"/>
-      <c r="F181" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G181" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K181" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="M181" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N181" s="2"/>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q181" s="2"/>
-      <c r="R181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF181" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG181" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH181" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI181" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ181" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5513" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="440">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:17:49+00:00</t>
+    <t>2026-09-12T17:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,10 +631,23 @@
     <t>Beobachtete Morphologie (SNOMED CT).</t>
   </si>
   <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.Menge[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+QuantityRange</t>
+  </si>
+  <si>
+    <t>Menge</t>
+  </si>
+  <si>
+    <t>Wie viel des berichteten Befunds gesehen wurde: als semiquantitative Stufe (SNOMED CT) oder als Zählung je Gesichtsfeld (UCUM).</t>
+  </si>
+  <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.AllgemeineMikroskopie.Untersuchungsmethode</t>
   </si>
   <si>
-    <t>Eingesetztes mikroskopisches Verfahren einschließlich Färbetechnik, z. B. Gramfärbung (SNOMED CT).</t>
+    <t>Eingesetztes mikroskopisches Verfahren (SNOMED CT). Die Färbetechnik wird daneben angegeben.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie</t>
@@ -643,7 +656,7 @@
     <t>Spezifische Mikroskopie</t>
   </si>
   <si>
-    <t>Mikroskopischer Nachweis eines im Untersuchungscode benannten Objekts mit der semiquantitativen Stufe als Ergebnis.</t>
+    <t>Mikroskopischer Nachweis eines im Untersuchungscode benannten Objekts; die Menge des Gesehenen wird daneben angegeben.</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.id</t>
@@ -664,13 +677,19 @@
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Ergebnis</t>
   </si>
   <si>
-    <t>Semiquantitative Stufe, in der das gesuchte Objekt gesehen wurde (SNOMED CT).</t>
+    <t>Nachweis oder Ausschluss des gesuchten Objekts (SNOMED CT).</t>
+  </si>
+  <si>
+    <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Menge[x]</t>
+  </si>
+  <si>
+    <t>Wie viel des nachgewiesenen Objekts gesehen wurde: als semiquantitative Stufe (SNOMED CT) oder als Zählung je Gesichtsfeld (UCUM).</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.SpezifischeMikroskopie.Untersuchungsmethode</t>
   </si>
   <si>
-    <t>Eingesetzte Färbetechnik, entbehrlich wenn sie bereits im Untersuchungscode steht (SNOMED CT).</t>
+    <t>Eingesetztes mikroskopisches Verfahren (SNOMED CT).</t>
   </si>
   <si>
     <t>mii-lm-mikrobio-untersuchungsarten.Kultur.BartlettScore</t>
@@ -1640,7 +1659,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ174"/>
+  <dimension ref="A1:AJ176"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="97.9765625" customWidth="true" bestFit="true"/>
@@ -5444,13 +5463,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5518,10 +5537,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5532,7 +5551,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -5544,13 +5563,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5601,27 +5620,27 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5632,7 +5651,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -5644,13 +5663,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>86</v>
+        <v>207</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5701,38 +5720,38 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>87</v>
+        <v>205</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5744,17 +5763,15 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -5791,43 +5808,43 @@
         <v>73</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -5840,26 +5857,24 @@
         <v>73</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>90</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="O42" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>73</v>
       </c>
@@ -5895,19 +5910,19 @@
         <v>73</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5924,42 +5939,46 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>73</v>
       </c>
@@ -6007,27 +6026,27 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>207</v>
+        <v>153</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6035,7 +6054,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>83</v>
@@ -6053,10 +6072,10 @@
         <v>180</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6107,10 +6126,10 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>83</v>
@@ -6124,10 +6143,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6153,10 +6172,10 @@
         <v>180</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6207,7 +6226,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6224,10 +6243,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6238,7 +6257,7 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>73</v>
@@ -6250,13 +6269,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6307,27 +6326,27 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6350,13 +6369,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6407,7 +6426,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>87</v>
+        <v>217</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6424,14 +6443,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6450,17 +6469,15 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>73</v>
@@ -6497,19 +6514,19 @@
         <v>73</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6521,51 +6538,47 @@
         <v>73</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
       </c>
@@ -6613,38 +6626,38 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>73</v>
@@ -6656,15 +6669,17 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
@@ -6701,71 +6716,75 @@
         <v>73</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>73</v>
       </c>
@@ -6813,27 +6832,27 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>221</v>
+        <v>153</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6841,7 +6860,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>83</v>
@@ -6859,10 +6878,10 @@
         <v>180</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6913,10 +6932,10 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>83</v>
@@ -6930,10 +6949,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6944,7 +6963,7 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
@@ -6956,13 +6975,13 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>226</v>
+        <v>184</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7013,27 +7032,27 @@
         <v>73</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7056,13 +7075,13 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7113,7 +7132,7 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7130,14 +7149,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7156,17 +7175,15 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>91</v>
+        <v>232</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7203,19 +7220,19 @@
         <v>73</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>97</v>
+        <v>231</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7227,51 +7244,47 @@
         <v>73</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>73</v>
       </c>
@@ -7319,38 +7332,38 @@
         <v>73</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
@@ -7362,15 +7375,17 @@
         <v>73</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>73</v>
@@ -7407,71 +7422,75 @@
         <v>73</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>231</v>
+        <v>97</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>73</v>
       </c>
@@ -7519,27 +7538,27 @@
         <v>73</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>233</v>
+        <v>153</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7547,7 +7566,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>83</v>
@@ -7565,10 +7584,10 @@
         <v>180</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7619,10 +7638,10 @@
         <v>73</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>83</v>
@@ -7636,10 +7655,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7650,7 +7669,7 @@
         <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>73</v>
@@ -7662,13 +7681,13 @@
         <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7719,27 +7738,27 @@
         <v>73</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7762,13 +7781,13 @@
         <v>73</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7819,7 +7838,7 @@
         <v>73</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -7836,14 +7855,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -7862,17 +7881,15 @@
         <v>73</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>73</v>
@@ -7909,19 +7926,19 @@
         <v>73</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -7933,51 +7950,47 @@
         <v>73</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>73</v>
       </c>
@@ -8025,38 +8038,38 @@
         <v>73</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>73</v>
@@ -8068,15 +8081,17 @@
         <v>73</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>73</v>
@@ -8113,71 +8128,75 @@
         <v>73</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>243</v>
+        <v>97</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>73</v>
       </c>
@@ -8225,27 +8244,27 @@
         <v>73</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>245</v>
+        <v>153</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8253,7 +8272,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>83</v>
@@ -8271,10 +8290,10 @@
         <v>180</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8325,10 +8344,10 @@
         <v>73</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>83</v>
@@ -8342,10 +8361,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8368,13 +8387,13 @@
         <v>73</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8425,7 +8444,7 @@
         <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
@@ -8442,10 +8461,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8456,7 +8475,7 @@
         <v>74</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>73</v>
@@ -8468,13 +8487,13 @@
         <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8525,27 +8544,27 @@
         <v>73</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8568,13 +8587,13 @@
         <v>73</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>86</v>
+        <v>257</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8625,7 +8644,7 @@
         <v>73</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>87</v>
+        <v>256</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -8642,14 +8661,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -8668,17 +8687,15 @@
         <v>73</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>91</v>
+        <v>259</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>73</v>
@@ -8715,19 +8732,19 @@
         <v>73</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -8739,51 +8756,47 @@
         <v>73</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>73</v>
       </c>
@@ -8831,38 +8844,38 @@
         <v>73</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>73</v>
@@ -8874,15 +8887,17 @@
         <v>73</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>73</v>
@@ -8919,71 +8934,75 @@
         <v>73</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>258</v>
+        <v>97</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>261</v>
+        <v>90</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>73</v>
       </c>
@@ -9031,27 +9050,27 @@
         <v>73</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>260</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9059,7 +9078,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>83</v>
@@ -9074,13 +9093,13 @@
         <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9131,10 +9150,10 @@
         <v>73</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>83</v>
@@ -9143,15 +9162,15 @@
         <v>73</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9174,13 +9193,13 @@
         <v>73</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9231,7 +9250,7 @@
         <v>73</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -9248,21 +9267,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>73</v>
@@ -9274,17 +9293,15 @@
         <v>73</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>73</v>
@@ -9321,75 +9338,71 @@
         <v>73</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>97</v>
+        <v>269</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>73</v>
       </c>
@@ -9437,38 +9450,38 @@
         <v>73</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>73</v>
@@ -9480,15 +9493,17 @@
         <v>73</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>269</v>
+        <v>91</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>73</v>
@@ -9525,71 +9540,75 @@
         <v>73</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>268</v>
+        <v>97</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>272</v>
+        <v>150</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>73</v>
       </c>
@@ -9637,19 +9656,19 @@
         <v>73</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80">
@@ -9665,10 +9684,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>73</v>
@@ -9680,7 +9699,7 @@
         <v>73</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L80" t="s" s="2">
         <v>275</v>
@@ -9740,16 +9759,16 @@
         <v>274</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -9765,7 +9784,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>83</v>
@@ -9780,13 +9799,13 @@
         <v>73</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>86</v>
+        <v>279</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9837,10 +9856,10 @@
         <v>73</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>87</v>
+        <v>277</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>83</v>
@@ -9854,14 +9873,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -9880,17 +9899,15 @@
         <v>73</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>91</v>
+        <v>281</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>73</v>
@@ -9927,19 +9944,19 @@
         <v>73</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>74</v>
@@ -9951,51 +9968,47 @@
         <v>73</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>73</v>
       </c>
@@ -10043,31 +10056,31 @@
         <v>73</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10086,15 +10099,17 @@
         <v>73</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>281</v>
+        <v>91</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>73</v>
@@ -10131,19 +10146,19 @@
         <v>73</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>280</v>
+        <v>97</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10155,47 +10170,51 @@
         <v>73</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>73</v>
       </c>
@@ -10243,31 +10262,31 @@
         <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10286,17 +10305,15 @@
         <v>73</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>91</v>
+        <v>287</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>73</v>
@@ -10333,19 +10350,19 @@
         <v>73</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>97</v>
+        <v>286</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10357,51 +10374,47 @@
         <v>73</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>73</v>
       </c>
@@ -10449,38 +10462,38 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>73</v>
@@ -10492,15 +10505,17 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>73</v>
@@ -10537,71 +10552,75 @@
         <v>73</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>73</v>
       </c>
@@ -10649,27 +10668,27 @@
         <v>73</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>288</v>
+        <v>153</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10677,7 +10696,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>83</v>
@@ -10695,10 +10714,10 @@
         <v>180</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10749,10 +10768,10 @@
         <v>73</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>83</v>
@@ -10766,10 +10785,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10780,7 +10799,7 @@
         <v>74</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>73</v>
@@ -10792,13 +10811,13 @@
         <v>73</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>293</v>
+        <v>184</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10849,27 +10868,27 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10892,13 +10911,13 @@
         <v>73</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>86</v>
+        <v>297</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -10949,7 +10968,7 @@
         <v>73</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>87</v>
+        <v>296</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -10966,14 +10985,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -10992,17 +11011,15 @@
         <v>73</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>91</v>
+        <v>299</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>73</v>
@@ -11039,19 +11056,19 @@
         <v>73</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>97</v>
+        <v>298</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -11063,51 +11080,47 @@
         <v>73</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>73</v>
       </c>
@@ -11155,38 +11168,38 @@
         <v>73</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>73</v>
@@ -11198,15 +11211,17 @@
         <v>73</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>73</v>
@@ -11243,71 +11258,75 @@
         <v>73</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>298</v>
+        <v>97</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>73</v>
       </c>
@@ -11355,27 +11374,27 @@
         <v>73</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>300</v>
+        <v>153</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11383,7 +11402,7 @@
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>83</v>
@@ -11401,10 +11420,10 @@
         <v>180</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11455,10 +11474,10 @@
         <v>73</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>83</v>
@@ -11472,10 +11491,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11486,7 +11505,7 @@
         <v>74</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>73</v>
@@ -11498,13 +11517,13 @@
         <v>73</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>305</v>
+        <v>184</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11555,27 +11574,27 @@
         <v>73</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11598,13 +11617,13 @@
         <v>73</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11655,7 +11674,7 @@
         <v>73</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>87</v>
+        <v>308</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -11672,14 +11691,14 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -11698,17 +11717,15 @@
         <v>73</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>91</v>
+        <v>311</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>73</v>
@@ -11745,19 +11762,19 @@
         <v>73</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>97</v>
+        <v>310</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -11769,51 +11786,47 @@
         <v>73</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>73</v>
       </c>
@@ -11861,38 +11874,38 @@
         <v>73</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>73</v>
@@ -11904,15 +11917,17 @@
         <v>73</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>73</v>
@@ -11949,71 +11964,75 @@
         <v>73</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>310</v>
+        <v>97</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>73</v>
       </c>
@@ -12061,27 +12080,27 @@
         <v>73</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>312</v>
+        <v>153</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12089,7 +12108,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>83</v>
@@ -12107,10 +12126,10 @@
         <v>180</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12161,10 +12180,10 @@
         <v>73</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>83</v>
@@ -12178,10 +12197,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12192,7 +12211,7 @@
         <v>74</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>73</v>
@@ -12204,13 +12223,13 @@
         <v>73</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>317</v>
+        <v>184</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12261,13 +12280,13 @@
         <v>73</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>73</v>
@@ -12278,10 +12297,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12292,7 +12311,7 @@
         <v>74</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>73</v>
@@ -12304,10 +12323,10 @@
         <v>73</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>320</v>
+        <v>187</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>321</v>
@@ -12361,19 +12380,19 @@
         <v>73</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
@@ -12392,7 +12411,7 @@
         <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>73</v>
@@ -12404,13 +12423,13 @@
         <v>73</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>85</v>
+        <v>323</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>86</v>
+        <v>324</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12461,13 +12480,13 @@
         <v>73</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>87</v>
+        <v>322</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>73</v>
@@ -12478,14 +12497,14 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -12504,17 +12523,15 @@
         <v>73</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>73</v>
@@ -12551,19 +12568,19 @@
         <v>73</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>97</v>
+        <v>325</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -12575,51 +12592,47 @@
         <v>73</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I109" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>73</v>
       </c>
@@ -12667,31 +12680,31 @@
         <v>73</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -12710,15 +12723,17 @@
         <v>73</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>326</v>
+        <v>91</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>73</v>
@@ -12755,19 +12770,19 @@
         <v>73</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>325</v>
+        <v>97</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>74</v>
@@ -12779,47 +12794,51 @@
         <v>73</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>73</v>
       </c>
@@ -12867,31 +12886,31 @@
         <v>73</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -12910,17 +12929,15 @@
         <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>91</v>
+        <v>332</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>73</v>
@@ -12957,19 +12974,19 @@
         <v>73</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>97</v>
+        <v>331</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -12981,51 +12998,47 @@
         <v>73</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>73</v>
       </c>
@@ -13073,38 +13086,38 @@
         <v>73</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>73</v>
@@ -13116,15 +13129,17 @@
         <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>73</v>
@@ -13161,71 +13176,75 @@
         <v>73</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>331</v>
+        <v>97</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>73</v>
       </c>
@@ -13273,27 +13292,27 @@
         <v>73</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>333</v>
+        <v>153</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13301,10 +13320,10 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>73</v>
@@ -13316,13 +13335,13 @@
         <v>73</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>336</v>
+        <v>181</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -13373,27 +13392,27 @@
         <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13416,13 +13435,13 @@
         <v>73</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>86</v>
+        <v>340</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13473,7 +13492,7 @@
         <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>87</v>
+        <v>339</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -13490,14 +13509,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -13516,17 +13535,15 @@
         <v>73</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>91</v>
+        <v>342</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>73</v>
@@ -13563,19 +13580,19 @@
         <v>73</v>
       </c>
       <c r="AB118" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC118" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE118" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>97</v>
+        <v>341</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -13587,51 +13604,47 @@
         <v>73</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>73</v>
       </c>
@@ -13679,38 +13692,38 @@
         <v>73</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>73</v>
@@ -13722,15 +13735,17 @@
         <v>73</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>73</v>
@@ -13767,71 +13782,75 @@
         <v>73</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>341</v>
+        <v>97</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>73</v>
       </c>
@@ -13879,27 +13898,27 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>343</v>
+        <v>153</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13907,7 +13926,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>83</v>
@@ -13925,10 +13944,10 @@
         <v>180</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>303</v>
+        <v>348</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13979,10 +13998,10 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>83</v>
@@ -13996,10 +14015,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14010,7 +14029,7 @@
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>73</v>
@@ -14022,13 +14041,13 @@
         <v>73</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>346</v>
+        <v>184</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14079,27 +14098,27 @@
         <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14122,13 +14141,13 @@
         <v>73</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14179,7 +14198,7 @@
         <v>73</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>87</v>
+        <v>350</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -14196,14 +14215,14 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -14222,17 +14241,15 @@
         <v>73</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>91</v>
+        <v>352</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>73</v>
@@ -14269,19 +14286,19 @@
         <v>73</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>97</v>
+        <v>351</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -14293,51 +14310,47 @@
         <v>73</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>73</v>
       </c>
@@ -14385,38 +14398,38 @@
         <v>73</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>73</v>
@@ -14428,15 +14441,17 @@
         <v>73</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N127" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>73</v>
@@ -14473,71 +14488,75 @@
         <v>73</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC127" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD127" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>351</v>
+        <v>97</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I128" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P128" t="s" s="2">
         <v>73</v>
       </c>
@@ -14585,27 +14604,27 @@
         <v>73</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>353</v>
+        <v>153</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14613,10 +14632,10 @@
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14628,13 +14647,13 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>356</v>
+        <v>181</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14685,27 +14704,27 @@
         <v>73</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14728,13 +14747,13 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>86</v>
+        <v>360</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -14785,7 +14804,7 @@
         <v>73</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>87</v>
+        <v>359</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -14802,14 +14821,14 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -14828,17 +14847,15 @@
         <v>73</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>91</v>
+        <v>362</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N131" s="2"/>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>73</v>
@@ -14875,19 +14892,19 @@
         <v>73</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>97</v>
+        <v>361</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -14899,51 +14916,47 @@
         <v>73</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>73</v>
       </c>
@@ -14991,38 +15004,38 @@
         <v>73</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>73</v>
@@ -15034,15 +15047,17 @@
         <v>73</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>73</v>
@@ -15079,71 +15094,75 @@
         <v>73</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC133" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>361</v>
+        <v>97</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O134" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P134" t="s" s="2">
         <v>73</v>
       </c>
@@ -15191,27 +15210,27 @@
         <v>73</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>363</v>
+        <v>153</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15219,10 +15238,10 @@
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>73</v>
@@ -15234,13 +15253,13 @@
         <v>73</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>366</v>
+        <v>181</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15291,27 +15310,27 @@
         <v>73</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15334,13 +15353,13 @@
         <v>73</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>86</v>
+        <v>370</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15391,7 +15410,7 @@
         <v>73</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>87</v>
+        <v>369</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -15408,14 +15427,14 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -15434,17 +15453,15 @@
         <v>73</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>91</v>
+        <v>372</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>73</v>
@@ -15481,19 +15498,19 @@
         <v>73</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>97</v>
+        <v>371</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
@@ -15505,51 +15522,47 @@
         <v>73</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G138" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H138" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>73</v>
       </c>
@@ -15597,38 +15610,38 @@
         <v>73</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>73</v>
@@ -15640,15 +15653,17 @@
         <v>73</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N139" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>73</v>
@@ -15685,71 +15700,75 @@
         <v>73</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>371</v>
+        <v>97</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J140" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P140" t="s" s="2">
         <v>73</v>
       </c>
@@ -15797,27 +15816,27 @@
         <v>73</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>373</v>
+        <v>153</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15825,10 +15844,10 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>73</v>
@@ -15840,13 +15859,13 @@
         <v>73</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>376</v>
+        <v>181</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -15897,13 +15916,13 @@
         <v>73</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>73</v>
@@ -15914,10 +15933,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -15928,7 +15947,7 @@
         <v>74</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>73</v>
@@ -15940,10 +15959,10 @@
         <v>73</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>379</v>
+        <v>184</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>380</v>
@@ -15997,19 +16016,19 @@
         <v>73</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="143">
@@ -16028,7 +16047,7 @@
         <v>74</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>73</v>
@@ -16040,13 +16059,13 @@
         <v>73</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>85</v>
+        <v>382</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>86</v>
+        <v>383</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16097,13 +16116,13 @@
         <v>73</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>87</v>
+        <v>381</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>73</v>
@@ -16114,14 +16133,14 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -16140,17 +16159,15 @@
         <v>73</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>91</v>
+        <v>385</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>73</v>
@@ -16187,19 +16204,19 @@
         <v>73</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>97</v>
+        <v>384</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>74</v>
@@ -16211,51 +16228,47 @@
         <v>73</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>73</v>
       </c>
@@ -16303,38 +16316,38 @@
         <v>73</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>73</v>
@@ -16346,15 +16359,17 @@
         <v>73</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N146" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N146" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>73</v>
@@ -16391,71 +16406,75 @@
         <v>73</v>
       </c>
       <c r="AB146" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC146" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD146" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE146" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>384</v>
+        <v>97</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I147" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O147" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P147" t="s" s="2">
         <v>73</v>
       </c>
@@ -16503,27 +16522,27 @@
         <v>73</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>386</v>
+        <v>153</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16531,7 +16550,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>83</v>
@@ -16549,10 +16568,10 @@
         <v>180</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>248</v>
+        <v>181</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16603,10 +16622,10 @@
         <v>73</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>83</v>
@@ -16620,10 +16639,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16646,13 +16665,13 @@
         <v>73</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -16703,7 +16722,7 @@
         <v>73</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
@@ -16720,10 +16739,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16734,7 +16753,7 @@
         <v>74</v>
       </c>
       <c r="G150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>73</v>
@@ -16746,13 +16765,13 @@
         <v>73</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>393</v>
+        <v>254</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -16803,27 +16822,27 @@
         <v>73</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16846,13 +16865,13 @@
         <v>73</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>86</v>
+        <v>397</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -16903,7 +16922,7 @@
         <v>73</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>87</v>
+        <v>396</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -16920,14 +16939,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -16946,17 +16965,15 @@
         <v>73</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>91</v>
+        <v>399</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
         <v>73</v>
@@ -16993,19 +17010,19 @@
         <v>73</v>
       </c>
       <c r="AB152" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC152" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD152" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE152" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>97</v>
+        <v>398</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
@@ -17017,51 +17034,47 @@
         <v>73</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
         <v>73</v>
       </c>
@@ -17109,31 +17122,31 @@
         <v>73</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
@@ -17152,15 +17165,17 @@
         <v>73</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>399</v>
+        <v>91</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N154" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>73</v>
@@ -17197,19 +17212,19 @@
         <v>73</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>398</v>
+        <v>97</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
@@ -17221,47 +17236,51 @@
         <v>73</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N155" s="2"/>
-      <c r="O155" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P155" t="s" s="2">
         <v>73</v>
       </c>
@@ -17309,31 +17328,31 @@
         <v>73</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>87</v>
+        <v>153</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ155" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -17352,17 +17371,15 @@
         <v>73</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>91</v>
+        <v>405</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>73</v>
@@ -17399,19 +17416,19 @@
         <v>73</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>97</v>
+        <v>404</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>74</v>
@@ -17423,51 +17440,47 @@
         <v>73</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>73</v>
       </c>
@@ -17515,38 +17528,38 @@
         <v>73</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>73</v>
@@ -17558,15 +17571,17 @@
         <v>73</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N158" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>73</v>
@@ -17603,71 +17618,75 @@
         <v>73</v>
       </c>
       <c r="AB158" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC158" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD158" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE158" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I159" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N159" s="2"/>
-      <c r="O159" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N159" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>73</v>
       </c>
@@ -17715,27 +17734,27 @@
         <v>73</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>406</v>
+        <v>153</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17743,7 +17762,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>83</v>
@@ -17761,10 +17780,10 @@
         <v>180</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -17815,10 +17834,10 @@
         <v>73</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>83</v>
@@ -17832,10 +17851,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -17846,7 +17865,7 @@
         <v>74</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>73</v>
@@ -17858,13 +17877,13 @@
         <v>73</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>410</v>
+        <v>184</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -17915,27 +17934,27 @@
         <v>73</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -17958,13 +17977,13 @@
         <v>73</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>86</v>
+        <v>397</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18015,7 +18034,7 @@
         <v>73</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>87</v>
+        <v>414</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>74</v>
@@ -18032,14 +18051,14 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
@@ -18058,17 +18077,15 @@
         <v>73</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>91</v>
+        <v>416</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
         <v>73</v>
@@ -18105,19 +18122,19 @@
         <v>73</v>
       </c>
       <c r="AB163" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC163" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD163" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE163" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>97</v>
+        <v>415</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>74</v>
@@ -18129,51 +18146,47 @@
         <v>73</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I164" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N164" s="2"/>
+      <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
         <v>73</v>
       </c>
@@ -18221,38 +18234,38 @@
         <v>73</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>73</v>
@@ -18264,15 +18277,17 @@
         <v>73</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N165" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>73</v>
@@ -18309,71 +18324,75 @@
         <v>73</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC165" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD165" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>415</v>
+        <v>97</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH165" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI165" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I166" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J166" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>418</v>
+        <v>90</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P166" t="s" s="2">
         <v>73</v>
       </c>
@@ -18421,27 +18440,27 @@
         <v>73</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>417</v>
+        <v>153</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18449,7 +18468,7 @@
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>83</v>
@@ -18467,10 +18486,10 @@
         <v>180</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18521,10 +18540,10 @@
         <v>73</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>83</v>
@@ -18538,10 +18557,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18552,7 +18571,7 @@
         <v>74</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>73</v>
@@ -18564,13 +18583,13 @@
         <v>73</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>141</v>
+        <v>424</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>423</v>
+        <v>184</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18621,27 +18640,27 @@
         <v>73</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18664,13 +18683,13 @@
         <v>73</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>86</v>
+        <v>427</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -18721,7 +18740,7 @@
         <v>73</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>87</v>
+        <v>426</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>74</v>
@@ -18738,14 +18757,14 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -18764,17 +18783,15 @@
         <v>73</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>91</v>
+        <v>429</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N170" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>73</v>
@@ -18811,19 +18828,19 @@
         <v>73</v>
       </c>
       <c r="AB170" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AC170" t="s" s="2">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="AD170" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>97</v>
+        <v>428</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>74</v>
@@ -18835,51 +18852,47 @@
         <v>73</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I171" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>73</v>
       </c>
@@ -18927,38 +18940,38 @@
         <v>73</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>73</v>
@@ -18970,15 +18983,17 @@
         <v>73</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>181</v>
+        <v>91</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N172" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>73</v>
@@ -19015,71 +19030,75 @@
         <v>73</v>
       </c>
       <c r="AB172" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AC172" t="s" s="2">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="AD172" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>428</v>
+        <v>97</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I173" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>234</v>
+        <v>90</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>73</v>
       </c>
@@ -19127,27 +19146,27 @@
         <v>73</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>430</v>
+        <v>153</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19155,7 +19174,7 @@
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G174" t="s" s="2">
         <v>83</v>
@@ -19173,10 +19192,10 @@
         <v>180</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19227,10 +19246,10 @@
         <v>73</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>83</v>
@@ -19239,6 +19258,206 @@
         <v>73</v>
       </c>
       <c r="AJ174" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E175" s="2"/>
+      <c r="F175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K175" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M175" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N175" s="2"/>
+      <c r="O175" s="2"/>
+      <c r="P175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q175" s="2"/>
+      <c r="R175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF175" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG175" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH175" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI175" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ175" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E176" s="2"/>
+      <c r="F176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K176" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L176" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M176" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N176" s="2"/>
+      <c r="O176" s="2"/>
+      <c r="P176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q176" s="2"/>
+      <c r="R176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG176" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH176" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI176" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ176" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/StructureDefinition-mii-lm-mikrobio-untersuchungsarten.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:15:10+00:00</t>
+    <t>2026-09-12T20:14:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
